--- a/InputData/elec/BPSpUGBCD/BAU Subsidy per Unit Grid Battery Capacity Deployed.xlsx
+++ b/InputData/elec/BPSpUGBCD/BAU Subsidy per Unit Grid Battery Capacity Deployed.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BPSpUGBCD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BSpUGBCD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7904D373-1906-4CBC-A10D-8F3D536CBA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50321F0-A6F9-48AB-8C5A-98FD513AF3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Inflation Reduction Act" sheetId="2" r:id="rId2"/>
-    <sheet name="BPSpUGBCD" sheetId="3" r:id="rId3"/>
+    <sheet name="Inflation Reduction Act" sheetId="7" r:id="rId2"/>
+    <sheet name="BPSpUGBCD" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,27 +34,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
-  <si>
-    <t>BPSpUGBCD BAU Percent Subsidy per Unit Grid Battery Capacity Deployed</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>Source:</t>
-  </si>
-  <si>
-    <t>See Inflation Reduction Act tab</t>
   </si>
   <si>
     <t>Notes:</t>
   </si>
   <si>
-    <t xml:space="preserve">This file assumes developers will opt for the battery ITC, given the </t>
+    <t>Dmnl</t>
+  </si>
+  <si>
+    <t>Percent of Capital Cost</t>
   </si>
   <si>
     <t>incentives in the Inflation Reduction Act. Given the volume of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This file assumes developers will opt for the battery ITC, given the </t>
   </si>
   <si>
     <t>announced battery manufacturing capacity, we assume projects</t>
@@ -111,7 +107,25 @@
     <t>Assumed that wind fully qualifies for domestic content credit, because weighted domestic content share is ~70%</t>
   </si>
   <si>
-    <t>Source: https://netzeroamerica.princeton.edu/img/Working_Paper-High_Road_Labor_and_Renewable_Energy-PUBLIC_RELEASE-4-13-21.pdf</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Source: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://netzeroamerica.princeton.edu/img/Working_Paper-High_Road_Labor_and_Renewable_Energy-PUBLIC_RELEASE-4-13-21.pdf</t>
+    </r>
   </si>
   <si>
     <t>Solar PV Capital Costs</t>
@@ -192,6 +206,21 @@
     <t>apply for any plant that begins construction in the applicable year rather than when plants come online).</t>
   </si>
   <si>
+    <t>Domestic content bonus, base</t>
+  </si>
+  <si>
+    <t>Domestic content bonus, bonus</t>
+  </si>
+  <si>
+    <t>Transferability penalty</t>
+  </si>
+  <si>
+    <t>Energy community bonus</t>
+  </si>
+  <si>
+    <t>Fraction of capacity qualifying for energy community bonus</t>
+  </si>
+  <si>
     <t>ITC</t>
   </si>
   <si>
@@ -207,31 +236,16 @@
     <t>Bonus Credit</t>
   </si>
   <si>
-    <t>Domestic content bonus, base</t>
-  </si>
-  <si>
-    <t>Domestic content bonus, bonus</t>
-  </si>
-  <si>
-    <t>Transferability penalty</t>
-  </si>
-  <si>
-    <t>Energy community bonus</t>
-  </si>
-  <si>
-    <t>Fraction of capacity qualifying for energy community bonus</t>
-  </si>
-  <si>
     <t>ITC Settings</t>
   </si>
   <si>
     <t>Offshore Credit Value % project costs</t>
   </si>
   <si>
-    <t>Dmnl</t>
+    <t>See Inflation Reduction Act tab</t>
   </si>
   <si>
-    <t>Percent of Capital Cost</t>
+    <t>BPSpUGBCD BAU Percent Subsidy per Unit Grid Battery Capacity Deployed</t>
   </si>
 </sst>
 </file>
@@ -243,7 +257,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,6 +338,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -463,8 +484,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -491,12 +512,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
@@ -508,7 +529,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -547,12 +568,12 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Currency 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Currency 2" xfId="5" xr:uid="{81BD210F-5FF0-4880-8028-0DC76957F95F}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{A0D66D47-893E-4339-ABA2-2AA2E8FD27AB}"/>
+    <cellStyle name="Normal 3 2" xfId="3" xr:uid="{6280AA9E-3B50-418D-82DE-98EB684B0878}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{2FFD538B-3558-46F7-AC70-5718F1F53027}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -565,6 +586,49 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3924300" cy="2562225"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image2.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5FB1B13-A2D0-4D9F-8AA7-389C0FFC2C37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28575" y="4972050"/>
+          <a:ext cx="3924300" cy="2562225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -859,23 +923,20 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -885,27 +946,27 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E9D1B2-CE7E-4A77-8E06-AF88043433CB}">
   <sheetPr>
     <tabColor rgb="FF6AA84F"/>
   </sheetPr>
@@ -920,13 +981,12 @@
     <col min="7" max="7" width="9.5703125" style="6" customWidth="1"/>
     <col min="8" max="8" width="10.140625" style="6" customWidth="1"/>
     <col min="9" max="36" width="7.5703125" style="6" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="6" customWidth="1"/>
-    <col min="38" max="16384" width="12.5703125" style="6"/>
+    <col min="37" max="16384" width="12.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -966,7 +1026,7 @@
     </row>
     <row r="2" spans="1:36" ht="305.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1004,7 +1064,7 @@
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
     </row>
-    <row r="3" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1042,9 +1102,9 @@
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
     </row>
-    <row r="4" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1082,9 +1142,9 @@
       <c r="AI4" s="8"/>
       <c r="AJ4" s="8"/>
     </row>
-    <row r="5" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1122,9 +1182,9 @@
       <c r="AI5" s="10"/>
       <c r="AJ5" s="10"/>
     </row>
-    <row r="6" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1162,9 +1222,9 @@
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5"/>
     </row>
-    <row r="7" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1202,7 +1262,7 @@
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
     </row>
-    <row r="8" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1240,7 +1300,7 @@
       <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
     </row>
-    <row r="9" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1278,7 +1338,7 @@
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1316,7 +1376,7 @@
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
     </row>
-    <row r="11" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1354,7 +1414,7 @@
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
     </row>
-    <row r="12" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1392,7 +1452,7 @@
       <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
     </row>
-    <row r="13" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1430,7 +1490,7 @@
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
     </row>
-    <row r="14" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="13"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1468,7 +1528,7 @@
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
     </row>
-    <row r="15" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1506,7 +1566,7 @@
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
     </row>
-    <row r="16" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1544,7 +1604,7 @@
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
     </row>
-    <row r="17" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1582,7 +1642,7 @@
       <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
     </row>
-    <row r="18" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1620,7 +1680,7 @@
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
     </row>
-    <row r="19" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1658,7 +1718,7 @@
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
     </row>
-    <row r="20" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1696,7 +1756,7 @@
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
     </row>
-    <row r="21" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1734,7 +1794,7 @@
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
     </row>
-    <row r="22" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1772,7 +1832,7 @@
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
     </row>
-    <row r="23" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1810,7 +1870,7 @@
       <c r="AI23" s="5"/>
       <c r="AJ23" s="5"/>
     </row>
-    <row r="24" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1848,7 +1908,7 @@
       <c r="AI24" s="5"/>
       <c r="AJ24" s="5"/>
     </row>
-    <row r="25" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1886,9 +1946,9 @@
       <c r="AI25" s="5"/>
       <c r="AJ25" s="5"/>
     </row>
-    <row r="26" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1926,9 +1986,9 @@
       <c r="AI26" s="5"/>
       <c r="AJ26" s="5"/>
     </row>
-    <row r="27" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1966,9 +2026,9 @@
       <c r="AI27" s="5"/>
       <c r="AJ27" s="5"/>
     </row>
-    <row r="28" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2006,9 +2066,9 @@
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
     </row>
-    <row r="29" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" s="14">
         <v>0.127</v>
@@ -2048,9 +2108,9 @@
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
     </row>
-    <row r="30" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="15">
         <f>B29*1.2</f>
@@ -2091,7 +2151,7 @@
       <c r="AI30" s="5"/>
       <c r="AJ30" s="5"/>
     </row>
-    <row r="31" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2129,7 +2189,7 @@
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
     </row>
-    <row r="32" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="13">
         <v>2022</v>
@@ -2225,9 +2285,9 @@
       <c r="AI32" s="5"/>
       <c r="AJ32" s="5"/>
     </row>
-    <row r="33" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" s="14">
         <v>0</v>
@@ -2323,9 +2383,9 @@
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
     </row>
-    <row r="34" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" s="14">
         <f>B33</f>
@@ -2422,7 +2482,7 @@
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
     </row>
-    <row r="35" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2460,9 +2520,9 @@
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
     </row>
-    <row r="36" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -2500,9 +2560,9 @@
       <c r="AI36" s="10"/>
       <c r="AJ36" s="10"/>
     </row>
-    <row r="37" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2540,9 +2600,9 @@
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
     </row>
-    <row r="38" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2580,7 +2640,7 @@
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
     </row>
-    <row r="39" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2618,16 +2678,16 @@
       <c r="AI39" s="5"/>
       <c r="AJ39" s="5"/>
     </row>
-    <row r="40" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="19" t="s">
         <v>25</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>26</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -2662,12 +2722,12 @@
       <c r="AI40" s="5"/>
       <c r="AJ40" s="5"/>
     </row>
-    <row r="41" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="21" t="s">
         <v>28</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>29</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -2704,9 +2764,9 @@
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
     </row>
-    <row r="42" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="23">
         <v>0.41199999999999998</v>
@@ -2748,9 +2808,9 @@
       <c r="AI42" s="5"/>
       <c r="AJ42" s="5"/>
     </row>
-    <row r="43" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="23">
         <v>0.13200000000000001</v>
@@ -2792,9 +2852,9 @@
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
     </row>
-    <row r="44" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" s="23">
         <v>0.114</v>
@@ -2836,9 +2896,9 @@
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
     </row>
-    <row r="45" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B45" s="23">
         <v>7.0000000000000007E-2</v>
@@ -2878,9 +2938,9 @@
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
     </row>
-    <row r="46" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" s="23">
         <v>8.7999999999999995E-2</v>
@@ -2920,9 +2980,9 @@
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
     </row>
-    <row r="47" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" s="23">
         <v>5.2999999999999999E-2</v>
@@ -2962,9 +3022,9 @@
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
     </row>
-    <row r="48" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="23">
         <v>4.3999999999999997E-2</v>
@@ -3004,9 +3064,9 @@
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
     </row>
-    <row r="49" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B49" s="23">
         <v>1.7999999999999999E-2</v>
@@ -3046,9 +3106,9 @@
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
     </row>
-    <row r="50" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="23">
         <v>2.5999999999999999E-2</v>
@@ -3088,9 +3148,9 @@
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
     </row>
-    <row r="51" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="26">
         <v>4.3999999999999997E-2</v>
@@ -3130,7 +3190,7 @@
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
     </row>
-    <row r="52" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="13"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -3168,9 +3228,9 @@
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
     </row>
-    <row r="53" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="24">
         <f>SUMPRODUCT(B42:B44,D42:D44)/SUM(B42:B44)</f>
@@ -3211,9 +3271,9 @@
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
     </row>
-    <row r="54" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="24">
         <f>AVERAGE(H62,B53)</f>
@@ -3254,7 +3314,7 @@
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
     </row>
-    <row r="55" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
       <c r="B55" s="24"/>
       <c r="C55" s="5"/>
@@ -3292,7 +3352,7 @@
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
     </row>
-    <row r="56" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
       <c r="B56" s="13">
         <v>2022</v>
@@ -3344,9 +3404,9 @@
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
     </row>
-    <row r="57" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="24">
         <f>B53</f>
@@ -3357,19 +3417,19 @@
         <v>0.16908814589665652</v>
       </c>
       <c r="D57" s="24">
-        <f>($H$57-$B$57)/5+C57</f>
+        <f t="shared" ref="D57:G57" si="0">($H$57-$B$57)/5+C57</f>
         <v>0.20717933130699087</v>
       </c>
       <c r="E57" s="24">
-        <f>($H$57-$B$57)/5+D57</f>
+        <f t="shared" si="0"/>
         <v>0.24527051671732522</v>
       </c>
       <c r="F57" s="24">
-        <f>($H$57-$B$57)/5+E57</f>
+        <f t="shared" si="0"/>
         <v>0.2833617021276596</v>
       </c>
       <c r="G57" s="24">
-        <f>($H$57-$B$57)/5+F57</f>
+        <f t="shared" si="0"/>
         <v>0.32145288753799395</v>
       </c>
       <c r="H57" s="24">
@@ -3404,7 +3464,7 @@
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
     </row>
-    <row r="58" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -3442,9 +3502,9 @@
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
     </row>
-    <row r="59" spans="1:36" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:36" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -3482,7 +3542,7 @@
       <c r="AI59" s="5"/>
       <c r="AJ59" s="5"/>
     </row>
-    <row r="60" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -3520,7 +3580,7 @@
       <c r="AI60" s="13"/>
       <c r="AJ60" s="13"/>
     </row>
-    <row r="61" spans="1:36" s="27" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:36" s="27" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="16"/>
       <c r="B61" s="16">
         <v>2022</v>
@@ -3616,9 +3676,9 @@
       <c r="AI61" s="13"/>
       <c r="AJ61" s="13"/>
     </row>
-    <row r="62" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" s="28">
         <v>0.4</v>
@@ -3714,9 +3774,9 @@
       <c r="AI62" s="24"/>
       <c r="AJ62" s="24"/>
     </row>
-    <row r="63" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" s="28">
         <f>B53</f>
@@ -3727,19 +3787,19 @@
         <v>0.20083080040526849</v>
       </c>
       <c r="D63" s="28">
-        <f>($H$63-$B$63)/COUNT($C$61:$H$61)+C63</f>
+        <f t="shared" ref="D63:G63" si="1">($H$63-$B$63)/COUNT($C$61:$H$61)+C63</f>
         <v>0.23257345491388046</v>
       </c>
       <c r="E63" s="28">
-        <f>($H$63-$B$63)/COUNT($C$61:$H$61)+D63</f>
+        <f t="shared" si="1"/>
         <v>0.2643161094224924</v>
       </c>
       <c r="F63" s="28">
-        <f>($H$63-$B$63)/COUNT($C$61:$H$61)+E63</f>
+        <f t="shared" si="1"/>
         <v>0.29605876393110436</v>
       </c>
       <c r="G63" s="28">
-        <f>($H$63-$B$63)/COUNT($C$61:$H$61)+F63</f>
+        <f t="shared" si="1"/>
         <v>0.32780141843971633</v>
       </c>
       <c r="H63" s="28">
@@ -3747,91 +3807,91 @@
         <v>0.3595440729483283</v>
       </c>
       <c r="I63" s="28">
-        <f t="shared" ref="I63:AD63" si="0">$H$63</f>
+        <f>$H$63</f>
         <v>0.3595440729483283</v>
       </c>
       <c r="J63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J63:AD63" si="2">$H$63</f>
         <v>0.3595440729483283</v>
       </c>
       <c r="K63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="L63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="M63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="N63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="O63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="P63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="Q63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="R63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="S63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="T63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="U63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="V63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="W63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="X63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="Y63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="Z63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="AA63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="AB63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="AC63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="AD63" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3595440729483283</v>
       </c>
       <c r="AE63" s="24"/>
@@ -3841,124 +3901,124 @@
       <c r="AI63" s="24"/>
       <c r="AJ63" s="24"/>
     </row>
-    <row r="64" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B64" s="28">
-        <f t="shared" ref="B64:AD64" si="1">B63/B62</f>
+        <f>B63/B62</f>
         <v>0.42272036474164126</v>
       </c>
       <c r="C64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C64:AD64" si="3">C63/C62</f>
         <v>0.50207700101317121</v>
       </c>
       <c r="D64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.5814336372847011</v>
       </c>
       <c r="E64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.66079027355623099</v>
       </c>
       <c r="F64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65790836429134303</v>
       </c>
       <c r="G64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65560283687943266</v>
       </c>
       <c r="H64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="I64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="J64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="K64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="L64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="M64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="N64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="O64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="P64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="Q64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="R64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="S64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="T64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="U64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="V64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="W64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="X64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="Y64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="Z64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="AA64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="AB64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="AC64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="AD64" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.65371649626968775</v>
       </c>
       <c r="AE64" s="5"/>
@@ -3968,7 +4028,7 @@
       <c r="AI64" s="5"/>
       <c r="AJ64" s="5"/>
     </row>
-    <row r="65" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="11"/>
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
@@ -4006,9 +4066,9 @@
       <c r="AI65" s="13"/>
       <c r="AJ65" s="13"/>
     </row>
-    <row r="66" spans="1:36" s="30" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:36" s="30" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B66" s="29">
         <v>1</v>
@@ -4104,7 +4164,7 @@
       <c r="AI66" s="16"/>
       <c r="AJ66" s="16"/>
     </row>
-    <row r="67" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="13"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
@@ -4142,9 +4202,9 @@
       <c r="AI67" s="13"/>
       <c r="AJ67" s="13"/>
     </row>
-    <row r="68" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
@@ -4182,9 +4242,9 @@
       <c r="AI68" s="10"/>
       <c r="AJ68" s="10"/>
     </row>
-    <row r="69" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -4222,9 +4282,9 @@
       <c r="AI69" s="5"/>
       <c r="AJ69" s="5"/>
     </row>
-    <row r="70" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -4262,9 +4322,9 @@
       <c r="AI70" s="5"/>
       <c r="AJ70" s="5"/>
     </row>
-    <row r="71" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -4302,7 +4362,7 @@
       <c r="AI71" s="5"/>
       <c r="AJ71" s="5"/>
     </row>
-    <row r="72" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -4340,9 +4400,9 @@
       <c r="AI72" s="5"/>
       <c r="AJ72" s="5"/>
     </row>
-    <row r="73" spans="1:36" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:36" s="36" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="33" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B73" s="39"/>
       <c r="C73" s="39"/>
@@ -4380,9 +4440,9 @@
       <c r="AI73" s="35"/>
       <c r="AJ73" s="35"/>
     </row>
-    <row r="74" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="31" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B74" s="31">
         <v>2022</v>
@@ -4478,9 +4538,9 @@
       <c r="AI74" s="5"/>
       <c r="AJ74" s="5"/>
     </row>
-    <row r="75" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="31" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B75" s="37">
         <v>0</v>
@@ -4576,7 +4636,7 @@
       <c r="AI75" s="5"/>
       <c r="AJ75" s="5"/>
     </row>
-    <row r="76" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="13"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -4614,9 +4674,9 @@
       <c r="AI76" s="5"/>
       <c r="AJ76" s="5"/>
     </row>
-    <row r="77" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="31" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B77" s="40">
         <v>0.06</v>
@@ -4656,9 +4716,9 @@
       <c r="AI77" s="5"/>
       <c r="AJ77" s="5"/>
     </row>
-    <row r="78" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="31" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B78" s="40">
         <v>0.3</v>
@@ -4698,9 +4758,9 @@
       <c r="AI78" s="5"/>
       <c r="AJ78" s="5"/>
     </row>
-    <row r="79" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="31" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B79" s="40">
         <v>0.02</v>
@@ -4740,9 +4800,9 @@
       <c r="AI79" s="5"/>
       <c r="AJ79" s="5"/>
     </row>
-    <row r="80" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="31" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B80" s="40">
         <v>0.1</v>
@@ -4782,9 +4842,9 @@
       <c r="AI80" s="5"/>
       <c r="AJ80" s="5"/>
     </row>
-    <row r="81" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B81" s="24">
         <v>7.4999999999999997E-2</v>
@@ -4824,9 +4884,9 @@
       <c r="AI81" s="5"/>
       <c r="AJ81" s="5"/>
     </row>
-    <row r="82" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="31" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B82" s="32">
         <v>0.1</v>
@@ -4866,9 +4926,9 @@
       <c r="AI82" s="5"/>
       <c r="AJ82" s="5"/>
     </row>
-    <row r="83" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="31" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B83" s="32">
         <v>0.5</v>
@@ -4908,7 +4968,7 @@
       <c r="AI83" s="5"/>
       <c r="AJ83" s="5"/>
     </row>
-    <row r="84" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="13"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -4946,9 +5006,9 @@
       <c r="AI84" s="5"/>
       <c r="AJ84" s="5"/>
     </row>
-    <row r="85" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -4986,7 +5046,7 @@
       <c r="AI85" s="5"/>
       <c r="AJ85" s="5"/>
     </row>
-    <row r="86" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="31"/>
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
@@ -5024,7 +5084,7 @@
       <c r="AI86" s="5"/>
       <c r="AJ86" s="5"/>
     </row>
-    <row r="87" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="31"/>
       <c r="B87" s="31">
         <v>2023</v>
@@ -5118,120 +5178,120 @@
       <c r="AI87" s="5"/>
       <c r="AJ87" s="5"/>
     </row>
-    <row r="88" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B88" s="38">
-        <f>C88</f>
+        <f t="shared" ref="B88:C88" si="4">C88</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="C88" s="38">
-        <f>D88</f>
+        <f t="shared" si="4"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="D88" s="38">
-        <f t="shared" ref="D88:AC88" si="2">(($B$78*C34+$B$77*(1-C34))+($B$80*C66+$B$79*(1-C66))+($B$82*$B$83))*(1-$B$81)*E75</f>
+        <f t="shared" ref="D88:AC88" si="5">(($B$78*C34+$B$77*(1-C34))+($B$80*C66+$B$79*(1-C66))+($B$82*$B$83))*(1-$B$81)*E75</f>
         <v>0.41625000000000001</v>
       </c>
       <c r="E88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="F88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="G88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="H88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="I88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="J88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="K88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="L88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="M88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="N88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="O88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.41625000000000001</v>
       </c>
       <c r="P88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.31218750000000001</v>
       </c>
       <c r="Q88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.208125</v>
       </c>
       <c r="R88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V88" s="38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD88" s="31"/>
@@ -5242,7 +5302,7 @@
       <c r="AI88" s="5"/>
       <c r="AJ88" s="5"/>
     </row>
-    <row r="89" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="13"/>
       <c r="B89" s="13"/>
       <c r="C89" s="13"/>
@@ -5280,7 +5340,7 @@
       <c r="AI89" s="13"/>
       <c r="AJ89" s="13"/>
     </row>
-    <row r="90" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -5318,7 +5378,7 @@
       <c r="AI90" s="5"/>
       <c r="AJ90" s="5"/>
     </row>
-    <row r="91" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -5356,7 +5416,7 @@
       <c r="AI91" s="5"/>
       <c r="AJ91" s="5"/>
     </row>
-    <row r="92" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -5394,7 +5454,7 @@
       <c r="AI92" s="5"/>
       <c r="AJ92" s="5"/>
     </row>
-    <row r="93" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -5432,7 +5492,7 @@
       <c r="AI93" s="5"/>
       <c r="AJ93" s="5"/>
     </row>
-    <row r="94" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -5470,7 +5530,7 @@
       <c r="AI94" s="5"/>
       <c r="AJ94" s="5"/>
     </row>
-    <row r="95" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -5508,7 +5568,7 @@
       <c r="AI95" s="5"/>
       <c r="AJ95" s="5"/>
     </row>
-    <row r="96" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -5546,7 +5606,7 @@
       <c r="AI96" s="5"/>
       <c r="AJ96" s="5"/>
     </row>
-    <row r="97" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -5584,7 +5644,7 @@
       <c r="AI97" s="5"/>
       <c r="AJ97" s="5"/>
     </row>
-    <row r="98" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -5622,7 +5682,7 @@
       <c r="AI98" s="5"/>
       <c r="AJ98" s="5"/>
     </row>
-    <row r="99" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -5660,7 +5720,7 @@
       <c r="AI99" s="5"/>
       <c r="AJ99" s="5"/>
     </row>
-    <row r="100" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -5698,7 +5758,7 @@
       <c r="AI100" s="5"/>
       <c r="AJ100" s="5"/>
     </row>
-    <row r="101" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -5736,7 +5796,7 @@
       <c r="AI101" s="5"/>
       <c r="AJ101" s="5"/>
     </row>
-    <row r="102" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -5774,7 +5834,7 @@
       <c r="AI102" s="5"/>
       <c r="AJ102" s="5"/>
     </row>
-    <row r="103" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -5812,7 +5872,7 @@
       <c r="AI103" s="5"/>
       <c r="AJ103" s="5"/>
     </row>
-    <row r="104" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -5850,7 +5910,7 @@
       <c r="AI104" s="5"/>
       <c r="AJ104" s="5"/>
     </row>
-    <row r="105" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -5888,7 +5948,7 @@
       <c r="AI105" s="5"/>
       <c r="AJ105" s="5"/>
     </row>
-    <row r="106" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -5926,7 +5986,7 @@
       <c r="AI106" s="5"/>
       <c r="AJ106" s="5"/>
     </row>
-    <row r="107" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -5964,7 +6024,7 @@
       <c r="AI107" s="5"/>
       <c r="AJ107" s="5"/>
     </row>
-    <row r="108" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -6002,7 +6062,7 @@
       <c r="AI108" s="5"/>
       <c r="AJ108" s="5"/>
     </row>
-    <row r="109" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -6040,7 +6100,7 @@
       <c r="AI109" s="5"/>
       <c r="AJ109" s="5"/>
     </row>
-    <row r="110" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -6078,7 +6138,7 @@
       <c r="AI110" s="5"/>
       <c r="AJ110" s="5"/>
     </row>
-    <row r="111" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -6116,7 +6176,7 @@
       <c r="AI111" s="5"/>
       <c r="AJ111" s="5"/>
     </row>
-    <row r="112" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -6154,7 +6214,7 @@
       <c r="AI112" s="5"/>
       <c r="AJ112" s="5"/>
     </row>
-    <row r="113" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -6192,7 +6252,7 @@
       <c r="AI113" s="5"/>
       <c r="AJ113" s="5"/>
     </row>
-    <row r="114" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -6230,7 +6290,7 @@
       <c r="AI114" s="5"/>
       <c r="AJ114" s="5"/>
     </row>
-    <row r="115" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -6268,7 +6328,7 @@
       <c r="AI115" s="5"/>
       <c r="AJ115" s="5"/>
     </row>
-    <row r="116" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -6306,7 +6366,7 @@
       <c r="AI116" s="5"/>
       <c r="AJ116" s="5"/>
     </row>
-    <row r="117" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -6344,7 +6404,7 @@
       <c r="AI117" s="5"/>
       <c r="AJ117" s="5"/>
     </row>
-    <row r="118" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -6382,7 +6442,7 @@
       <c r="AI118" s="5"/>
       <c r="AJ118" s="5"/>
     </row>
-    <row r="119" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -6420,7 +6480,7 @@
       <c r="AI119" s="5"/>
       <c r="AJ119" s="5"/>
     </row>
-    <row r="120" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -6458,7 +6518,7 @@
       <c r="AI120" s="5"/>
       <c r="AJ120" s="5"/>
     </row>
-    <row r="121" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -6496,7 +6556,7 @@
       <c r="AI121" s="5"/>
       <c r="AJ121" s="5"/>
     </row>
-    <row r="122" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -6534,7 +6594,7 @@
       <c r="AI122" s="5"/>
       <c r="AJ122" s="5"/>
     </row>
-    <row r="123" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -6572,7 +6632,7 @@
       <c r="AI123" s="5"/>
       <c r="AJ123" s="5"/>
     </row>
-    <row r="124" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -6610,7 +6670,7 @@
       <c r="AI124" s="5"/>
       <c r="AJ124" s="5"/>
     </row>
-    <row r="125" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -6648,7 +6708,7 @@
       <c r="AI125" s="5"/>
       <c r="AJ125" s="5"/>
     </row>
-    <row r="126" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -6686,7 +6746,7 @@
       <c r="AI126" s="5"/>
       <c r="AJ126" s="5"/>
     </row>
-    <row r="127" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -6724,7 +6784,7 @@
       <c r="AI127" s="5"/>
       <c r="AJ127" s="5"/>
     </row>
-    <row r="128" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -6762,7 +6822,7 @@
       <c r="AI128" s="5"/>
       <c r="AJ128" s="5"/>
     </row>
-    <row r="129" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -6800,7 +6860,7 @@
       <c r="AI129" s="5"/>
       <c r="AJ129" s="5"/>
     </row>
-    <row r="130" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -6838,7 +6898,7 @@
       <c r="AI130" s="5"/>
       <c r="AJ130" s="5"/>
     </row>
-    <row r="131" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -6876,7 +6936,7 @@
       <c r="AI131" s="5"/>
       <c r="AJ131" s="5"/>
     </row>
-    <row r="132" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -6914,7 +6974,7 @@
       <c r="AI132" s="5"/>
       <c r="AJ132" s="5"/>
     </row>
-    <row r="133" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -6952,7 +7012,7 @@
       <c r="AI133" s="5"/>
       <c r="AJ133" s="5"/>
     </row>
-    <row r="134" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -6990,7 +7050,7 @@
       <c r="AI134" s="5"/>
       <c r="AJ134" s="5"/>
     </row>
-    <row r="135" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -7028,7 +7088,7 @@
       <c r="AI135" s="5"/>
       <c r="AJ135" s="5"/>
     </row>
-    <row r="136" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -7066,7 +7126,7 @@
       <c r="AI136" s="5"/>
       <c r="AJ136" s="5"/>
     </row>
-    <row r="137" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -7104,7 +7164,7 @@
       <c r="AI137" s="5"/>
       <c r="AJ137" s="5"/>
     </row>
-    <row r="138" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -7142,7 +7202,7 @@
       <c r="AI138" s="5"/>
       <c r="AJ138" s="5"/>
     </row>
-    <row r="139" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -7180,7 +7240,7 @@
       <c r="AI139" s="5"/>
       <c r="AJ139" s="5"/>
     </row>
-    <row r="140" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -7218,7 +7278,7 @@
       <c r="AI140" s="5"/>
       <c r="AJ140" s="5"/>
     </row>
-    <row r="141" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -7256,7 +7316,7 @@
       <c r="AI141" s="5"/>
       <c r="AJ141" s="5"/>
     </row>
-    <row r="142" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -7294,7 +7354,7 @@
       <c r="AI142" s="5"/>
       <c r="AJ142" s="5"/>
     </row>
-    <row r="143" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -7332,7 +7392,7 @@
       <c r="AI143" s="5"/>
       <c r="AJ143" s="5"/>
     </row>
-    <row r="144" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -7370,7 +7430,7 @@
       <c r="AI144" s="5"/>
       <c r="AJ144" s="5"/>
     </row>
-    <row r="145" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -7408,7 +7468,7 @@
       <c r="AI145" s="5"/>
       <c r="AJ145" s="5"/>
     </row>
-    <row r="146" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -7446,7 +7506,7 @@
       <c r="AI146" s="5"/>
       <c r="AJ146" s="5"/>
     </row>
-    <row r="147" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -7484,7 +7544,7 @@
       <c r="AI147" s="5"/>
       <c r="AJ147" s="5"/>
     </row>
-    <row r="148" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -7522,7 +7582,7 @@
       <c r="AI148" s="5"/>
       <c r="AJ148" s="5"/>
     </row>
-    <row r="149" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -7560,7 +7620,7 @@
       <c r="AI149" s="5"/>
       <c r="AJ149" s="5"/>
     </row>
-    <row r="150" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -7598,7 +7658,7 @@
       <c r="AI150" s="5"/>
       <c r="AJ150" s="5"/>
     </row>
-    <row r="151" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -7636,7 +7696,7 @@
       <c r="AI151" s="5"/>
       <c r="AJ151" s="5"/>
     </row>
-    <row r="152" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -7674,7 +7734,7 @@
       <c r="AI152" s="5"/>
       <c r="AJ152" s="5"/>
     </row>
-    <row r="153" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -7712,7 +7772,7 @@
       <c r="AI153" s="5"/>
       <c r="AJ153" s="5"/>
     </row>
-    <row r="154" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -7750,7 +7810,7 @@
       <c r="AI154" s="5"/>
       <c r="AJ154" s="5"/>
     </row>
-    <row r="155" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -7788,7 +7848,7 @@
       <c r="AI155" s="5"/>
       <c r="AJ155" s="5"/>
     </row>
-    <row r="156" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -7826,7 +7886,7 @@
       <c r="AI156" s="5"/>
       <c r="AJ156" s="5"/>
     </row>
-    <row r="157" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -7864,7 +7924,7 @@
       <c r="AI157" s="5"/>
       <c r="AJ157" s="5"/>
     </row>
-    <row r="158" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -7902,7 +7962,7 @@
       <c r="AI158" s="5"/>
       <c r="AJ158" s="5"/>
     </row>
-    <row r="159" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -7940,7 +8000,7 @@
       <c r="AI159" s="5"/>
       <c r="AJ159" s="5"/>
     </row>
-    <row r="160" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -7978,7 +8038,7 @@
       <c r="AI160" s="5"/>
       <c r="AJ160" s="5"/>
     </row>
-    <row r="161" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -8016,7 +8076,7 @@
       <c r="AI161" s="5"/>
       <c r="AJ161" s="5"/>
     </row>
-    <row r="162" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -8054,7 +8114,7 @@
       <c r="AI162" s="5"/>
       <c r="AJ162" s="5"/>
     </row>
-    <row r="163" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -8092,7 +8152,7 @@
       <c r="AI163" s="5"/>
       <c r="AJ163" s="5"/>
     </row>
-    <row r="164" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -8130,7 +8190,7 @@
       <c r="AI164" s="5"/>
       <c r="AJ164" s="5"/>
     </row>
-    <row r="165" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -8168,7 +8228,7 @@
       <c r="AI165" s="5"/>
       <c r="AJ165" s="5"/>
     </row>
-    <row r="166" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -8206,7 +8266,7 @@
       <c r="AI166" s="5"/>
       <c r="AJ166" s="5"/>
     </row>
-    <row r="167" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -8244,7 +8304,7 @@
       <c r="AI167" s="5"/>
       <c r="AJ167" s="5"/>
     </row>
-    <row r="168" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -8282,7 +8342,7 @@
       <c r="AI168" s="5"/>
       <c r="AJ168" s="5"/>
     </row>
-    <row r="169" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -8320,7 +8380,7 @@
       <c r="AI169" s="5"/>
       <c r="AJ169" s="5"/>
     </row>
-    <row r="170" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -8358,7 +8418,7 @@
       <c r="AI170" s="5"/>
       <c r="AJ170" s="5"/>
     </row>
-    <row r="171" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -8396,7 +8456,7 @@
       <c r="AI171" s="5"/>
       <c r="AJ171" s="5"/>
     </row>
-    <row r="172" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -8434,7 +8494,7 @@
       <c r="AI172" s="5"/>
       <c r="AJ172" s="5"/>
     </row>
-    <row r="173" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -8472,7 +8532,7 @@
       <c r="AI173" s="5"/>
       <c r="AJ173" s="5"/>
     </row>
-    <row r="174" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -8510,7 +8570,7 @@
       <c r="AI174" s="5"/>
       <c r="AJ174" s="5"/>
     </row>
-    <row r="175" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -8548,7 +8608,7 @@
       <c r="AI175" s="5"/>
       <c r="AJ175" s="5"/>
     </row>
-    <row r="176" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -8586,7 +8646,7 @@
       <c r="AI176" s="5"/>
       <c r="AJ176" s="5"/>
     </row>
-    <row r="177" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -8624,7 +8684,7 @@
       <c r="AI177" s="5"/>
       <c r="AJ177" s="5"/>
     </row>
-    <row r="178" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -8662,7 +8722,7 @@
       <c r="AI178" s="5"/>
       <c r="AJ178" s="5"/>
     </row>
-    <row r="179" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -8700,7 +8760,7 @@
       <c r="AI179" s="5"/>
       <c r="AJ179" s="5"/>
     </row>
-    <row r="180" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -8738,7 +8798,7 @@
       <c r="AI180" s="5"/>
       <c r="AJ180" s="5"/>
     </row>
-    <row r="181" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -8776,7 +8836,7 @@
       <c r="AI181" s="5"/>
       <c r="AJ181" s="5"/>
     </row>
-    <row r="182" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -8814,7 +8874,7 @@
       <c r="AI182" s="5"/>
       <c r="AJ182" s="5"/>
     </row>
-    <row r="183" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -8852,7 +8912,7 @@
       <c r="AI183" s="5"/>
       <c r="AJ183" s="5"/>
     </row>
-    <row r="184" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -8890,7 +8950,7 @@
       <c r="AI184" s="5"/>
       <c r="AJ184" s="5"/>
     </row>
-    <row r="185" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -8928,7 +8988,7 @@
       <c r="AI185" s="5"/>
       <c r="AJ185" s="5"/>
     </row>
-    <row r="186" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -8966,7 +9026,7 @@
       <c r="AI186" s="5"/>
       <c r="AJ186" s="5"/>
     </row>
-    <row r="187" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -9004,7 +9064,7 @@
       <c r="AI187" s="5"/>
       <c r="AJ187" s="5"/>
     </row>
-    <row r="188" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -9042,7 +9102,7 @@
       <c r="AI188" s="5"/>
       <c r="AJ188" s="5"/>
     </row>
-    <row r="189" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -9080,7 +9140,7 @@
       <c r="AI189" s="5"/>
       <c r="AJ189" s="5"/>
     </row>
-    <row r="190" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -9118,7 +9178,7 @@
       <c r="AI190" s="5"/>
       <c r="AJ190" s="5"/>
     </row>
-    <row r="191" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -9156,7 +9216,7 @@
       <c r="AI191" s="5"/>
       <c r="AJ191" s="5"/>
     </row>
-    <row r="192" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -9194,7 +9254,7 @@
       <c r="AI192" s="5"/>
       <c r="AJ192" s="5"/>
     </row>
-    <row r="193" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -9232,7 +9292,7 @@
       <c r="AI193" s="5"/>
       <c r="AJ193" s="5"/>
     </row>
-    <row r="194" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -9270,7 +9330,7 @@
       <c r="AI194" s="5"/>
       <c r="AJ194" s="5"/>
     </row>
-    <row r="195" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -9308,7 +9368,7 @@
       <c r="AI195" s="5"/>
       <c r="AJ195" s="5"/>
     </row>
-    <row r="196" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -9346,7 +9406,7 @@
       <c r="AI196" s="5"/>
       <c r="AJ196" s="5"/>
     </row>
-    <row r="197" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -9384,7 +9444,7 @@
       <c r="AI197" s="5"/>
       <c r="AJ197" s="5"/>
     </row>
-    <row r="198" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -9422,7 +9482,7 @@
       <c r="AI198" s="5"/>
       <c r="AJ198" s="5"/>
     </row>
-    <row r="199" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -9460,7 +9520,7 @@
       <c r="AI199" s="5"/>
       <c r="AJ199" s="5"/>
     </row>
-    <row r="200" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -9498,7 +9558,7 @@
       <c r="AI200" s="5"/>
       <c r="AJ200" s="5"/>
     </row>
-    <row r="201" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -9536,7 +9596,7 @@
       <c r="AI201" s="5"/>
       <c r="AJ201" s="5"/>
     </row>
-    <row r="202" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -9574,7 +9634,7 @@
       <c r="AI202" s="5"/>
       <c r="AJ202" s="5"/>
     </row>
-    <row r="203" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -9612,7 +9672,7 @@
       <c r="AI203" s="5"/>
       <c r="AJ203" s="5"/>
     </row>
-    <row r="204" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -9650,7 +9710,7 @@
       <c r="AI204" s="5"/>
       <c r="AJ204" s="5"/>
     </row>
-    <row r="205" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -9688,7 +9748,7 @@
       <c r="AI205" s="5"/>
       <c r="AJ205" s="5"/>
     </row>
-    <row r="206" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -9726,7 +9786,7 @@
       <c r="AI206" s="5"/>
       <c r="AJ206" s="5"/>
     </row>
-    <row r="207" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -9764,7 +9824,7 @@
       <c r="AI207" s="5"/>
       <c r="AJ207" s="5"/>
     </row>
-    <row r="208" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -9802,7 +9862,7 @@
       <c r="AI208" s="5"/>
       <c r="AJ208" s="5"/>
     </row>
-    <row r="209" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -9840,7 +9900,7 @@
       <c r="AI209" s="5"/>
       <c r="AJ209" s="5"/>
     </row>
-    <row r="210" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -9878,7 +9938,7 @@
       <c r="AI210" s="5"/>
       <c r="AJ210" s="5"/>
     </row>
-    <row r="211" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -9916,7 +9976,7 @@
       <c r="AI211" s="5"/>
       <c r="AJ211" s="5"/>
     </row>
-    <row r="212" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -9954,7 +10014,7 @@
       <c r="AI212" s="5"/>
       <c r="AJ212" s="5"/>
     </row>
-    <row r="213" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -9992,7 +10052,7 @@
       <c r="AI213" s="5"/>
       <c r="AJ213" s="5"/>
     </row>
-    <row r="214" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -10030,7 +10090,7 @@
       <c r="AI214" s="5"/>
       <c r="AJ214" s="5"/>
     </row>
-    <row r="215" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -10068,7 +10128,7 @@
       <c r="AI215" s="5"/>
       <c r="AJ215" s="5"/>
     </row>
-    <row r="216" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -10106,7 +10166,7 @@
       <c r="AI216" s="5"/>
       <c r="AJ216" s="5"/>
     </row>
-    <row r="217" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -10144,7 +10204,7 @@
       <c r="AI217" s="5"/>
       <c r="AJ217" s="5"/>
     </row>
-    <row r="218" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -10182,7 +10242,7 @@
       <c r="AI218" s="5"/>
       <c r="AJ218" s="5"/>
     </row>
-    <row r="219" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -10220,7 +10280,7 @@
       <c r="AI219" s="5"/>
       <c r="AJ219" s="5"/>
     </row>
-    <row r="220" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -10258,7 +10318,7 @@
       <c r="AI220" s="5"/>
       <c r="AJ220" s="5"/>
     </row>
-    <row r="221" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -10296,7 +10356,7 @@
       <c r="AI221" s="5"/>
       <c r="AJ221" s="5"/>
     </row>
-    <row r="222" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -10334,7 +10394,7 @@
       <c r="AI222" s="5"/>
       <c r="AJ222" s="5"/>
     </row>
-    <row r="223" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -10372,7 +10432,7 @@
       <c r="AI223" s="5"/>
       <c r="AJ223" s="5"/>
     </row>
-    <row r="224" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -10410,7 +10470,7 @@
       <c r="AI224" s="5"/>
       <c r="AJ224" s="5"/>
     </row>
-    <row r="225" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -10448,7 +10508,7 @@
       <c r="AI225" s="5"/>
       <c r="AJ225" s="5"/>
     </row>
-    <row r="226" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -10486,7 +10546,7 @@
       <c r="AI226" s="5"/>
       <c r="AJ226" s="5"/>
     </row>
-    <row r="227" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -10524,7 +10584,7 @@
       <c r="AI227" s="5"/>
       <c r="AJ227" s="5"/>
     </row>
-    <row r="228" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -10562,7 +10622,7 @@
       <c r="AI228" s="5"/>
       <c r="AJ228" s="5"/>
     </row>
-    <row r="229" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -10600,7 +10660,7 @@
       <c r="AI229" s="5"/>
       <c r="AJ229" s="5"/>
     </row>
-    <row r="230" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -10638,7 +10698,7 @@
       <c r="AI230" s="5"/>
       <c r="AJ230" s="5"/>
     </row>
-    <row r="231" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -10676,7 +10736,7 @@
       <c r="AI231" s="5"/>
       <c r="AJ231" s="5"/>
     </row>
-    <row r="232" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -10714,7 +10774,7 @@
       <c r="AI232" s="5"/>
       <c r="AJ232" s="5"/>
     </row>
-    <row r="233" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -10752,7 +10812,7 @@
       <c r="AI233" s="5"/>
       <c r="AJ233" s="5"/>
     </row>
-    <row r="234" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -10790,7 +10850,7 @@
       <c r="AI234" s="5"/>
       <c r="AJ234" s="5"/>
     </row>
-    <row r="235" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -10828,7 +10888,7 @@
       <c r="AI235" s="5"/>
       <c r="AJ235" s="5"/>
     </row>
-    <row r="236" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -10866,7 +10926,7 @@
       <c r="AI236" s="5"/>
       <c r="AJ236" s="5"/>
     </row>
-    <row r="237" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -10904,7 +10964,7 @@
       <c r="AI237" s="5"/>
       <c r="AJ237" s="5"/>
     </row>
-    <row r="238" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -10942,7 +11002,7 @@
       <c r="AI238" s="5"/>
       <c r="AJ238" s="5"/>
     </row>
-    <row r="239" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -10980,7 +11040,7 @@
       <c r="AI239" s="5"/>
       <c r="AJ239" s="5"/>
     </row>
-    <row r="240" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -11018,7 +11078,7 @@
       <c r="AI240" s="5"/>
       <c r="AJ240" s="5"/>
     </row>
-    <row r="241" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -11056,7 +11116,7 @@
       <c r="AI241" s="5"/>
       <c r="AJ241" s="5"/>
     </row>
-    <row r="242" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -11094,7 +11154,7 @@
       <c r="AI242" s="5"/>
       <c r="AJ242" s="5"/>
     </row>
-    <row r="243" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -11132,7 +11192,7 @@
       <c r="AI243" s="5"/>
       <c r="AJ243" s="5"/>
     </row>
-    <row r="244" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -11170,7 +11230,7 @@
       <c r="AI244" s="5"/>
       <c r="AJ244" s="5"/>
     </row>
-    <row r="245" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -11208,7 +11268,7 @@
       <c r="AI245" s="5"/>
       <c r="AJ245" s="5"/>
     </row>
-    <row r="246" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -11246,7 +11306,7 @@
       <c r="AI246" s="5"/>
       <c r="AJ246" s="5"/>
     </row>
-    <row r="247" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -11284,7 +11344,7 @@
       <c r="AI247" s="5"/>
       <c r="AJ247" s="5"/>
     </row>
-    <row r="248" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -11322,7 +11382,7 @@
       <c r="AI248" s="5"/>
       <c r="AJ248" s="5"/>
     </row>
-    <row r="249" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -11360,7 +11420,7 @@
       <c r="AI249" s="5"/>
       <c r="AJ249" s="5"/>
     </row>
-    <row r="250" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -11398,7 +11458,7 @@
       <c r="AI250" s="5"/>
       <c r="AJ250" s="5"/>
     </row>
-    <row r="251" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -11436,7 +11496,7 @@
       <c r="AI251" s="5"/>
       <c r="AJ251" s="5"/>
     </row>
-    <row r="252" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -11474,7 +11534,7 @@
       <c r="AI252" s="5"/>
       <c r="AJ252" s="5"/>
     </row>
-    <row r="253" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -11512,7 +11572,7 @@
       <c r="AI253" s="5"/>
       <c r="AJ253" s="5"/>
     </row>
-    <row r="254" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -11550,7 +11610,7 @@
       <c r="AI254" s="5"/>
       <c r="AJ254" s="5"/>
     </row>
-    <row r="255" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -11588,7 +11648,7 @@
       <c r="AI255" s="5"/>
       <c r="AJ255" s="5"/>
     </row>
-    <row r="256" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -11626,7 +11686,7 @@
       <c r="AI256" s="5"/>
       <c r="AJ256" s="5"/>
     </row>
-    <row r="257" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -11664,7 +11724,7 @@
       <c r="AI257" s="5"/>
       <c r="AJ257" s="5"/>
     </row>
-    <row r="258" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -11702,7 +11762,7 @@
       <c r="AI258" s="5"/>
       <c r="AJ258" s="5"/>
     </row>
-    <row r="259" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -11740,7 +11800,7 @@
       <c r="AI259" s="5"/>
       <c r="AJ259" s="5"/>
     </row>
-    <row r="260" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -11778,7 +11838,7 @@
       <c r="AI260" s="5"/>
       <c r="AJ260" s="5"/>
     </row>
-    <row r="261" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -11816,7 +11876,7 @@
       <c r="AI261" s="5"/>
       <c r="AJ261" s="5"/>
     </row>
-    <row r="262" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -11854,7 +11914,7 @@
       <c r="AI262" s="5"/>
       <c r="AJ262" s="5"/>
     </row>
-    <row r="263" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -11892,7 +11952,7 @@
       <c r="AI263" s="5"/>
       <c r="AJ263" s="5"/>
     </row>
-    <row r="264" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -11930,7 +11990,7 @@
       <c r="AI264" s="5"/>
       <c r="AJ264" s="5"/>
     </row>
-    <row r="265" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -11968,7 +12028,7 @@
       <c r="AI265" s="5"/>
       <c r="AJ265" s="5"/>
     </row>
-    <row r="266" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -12006,7 +12066,7 @@
       <c r="AI266" s="5"/>
       <c r="AJ266" s="5"/>
     </row>
-    <row r="267" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -12044,7 +12104,7 @@
       <c r="AI267" s="5"/>
       <c r="AJ267" s="5"/>
     </row>
-    <row r="268" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -12082,7 +12142,7 @@
       <c r="AI268" s="5"/>
       <c r="AJ268" s="5"/>
     </row>
-    <row r="269" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -12120,7 +12180,7 @@
       <c r="AI269" s="5"/>
       <c r="AJ269" s="5"/>
     </row>
-    <row r="270" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -12158,7 +12218,7 @@
       <c r="AI270" s="5"/>
       <c r="AJ270" s="5"/>
     </row>
-    <row r="271" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -12196,7 +12256,7 @@
       <c r="AI271" s="5"/>
       <c r="AJ271" s="5"/>
     </row>
-    <row r="272" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -12234,7 +12294,7 @@
       <c r="AI272" s="5"/>
       <c r="AJ272" s="5"/>
     </row>
-    <row r="273" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -12272,7 +12332,7 @@
       <c r="AI273" s="5"/>
       <c r="AJ273" s="5"/>
     </row>
-    <row r="274" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -12310,7 +12370,7 @@
       <c r="AI274" s="5"/>
       <c r="AJ274" s="5"/>
     </row>
-    <row r="275" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -12348,7 +12408,7 @@
       <c r="AI275" s="5"/>
       <c r="AJ275" s="5"/>
     </row>
-    <row r="276" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -12386,7 +12446,7 @@
       <c r="AI276" s="5"/>
       <c r="AJ276" s="5"/>
     </row>
-    <row r="277" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -12424,7 +12484,7 @@
       <c r="AI277" s="5"/>
       <c r="AJ277" s="5"/>
     </row>
-    <row r="278" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -12462,7 +12522,7 @@
       <c r="AI278" s="5"/>
       <c r="AJ278" s="5"/>
     </row>
-    <row r="279" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -12500,7 +12560,7 @@
       <c r="AI279" s="5"/>
       <c r="AJ279" s="5"/>
     </row>
-    <row r="280" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -12538,7 +12598,7 @@
       <c r="AI280" s="5"/>
       <c r="AJ280" s="5"/>
     </row>
-    <row r="281" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -12576,7 +12636,7 @@
       <c r="AI281" s="5"/>
       <c r="AJ281" s="5"/>
     </row>
-    <row r="282" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -12614,7 +12674,7 @@
       <c r="AI282" s="5"/>
       <c r="AJ282" s="5"/>
     </row>
-    <row r="283" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -12652,7 +12712,7 @@
       <c r="AI283" s="5"/>
       <c r="AJ283" s="5"/>
     </row>
-    <row r="284" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -12690,7 +12750,7 @@
       <c r="AI284" s="5"/>
       <c r="AJ284" s="5"/>
     </row>
-    <row r="285" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -12728,7 +12788,7 @@
       <c r="AI285" s="5"/>
       <c r="AJ285" s="5"/>
     </row>
-    <row r="286" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -12766,7 +12826,7 @@
       <c r="AI286" s="5"/>
       <c r="AJ286" s="5"/>
     </row>
-    <row r="287" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -12804,7 +12864,7 @@
       <c r="AI287" s="5"/>
       <c r="AJ287" s="5"/>
     </row>
-    <row r="288" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -12842,7 +12902,7 @@
       <c r="AI288" s="5"/>
       <c r="AJ288" s="5"/>
     </row>
-    <row r="289" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -12880,7 +12940,7 @@
       <c r="AI289" s="5"/>
       <c r="AJ289" s="5"/>
     </row>
-    <row r="290" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -12918,7 +12978,7 @@
       <c r="AI290" s="5"/>
       <c r="AJ290" s="5"/>
     </row>
-    <row r="291" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -12956,7 +13016,7 @@
       <c r="AI291" s="5"/>
       <c r="AJ291" s="5"/>
     </row>
-    <row r="292" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -12994,7 +13054,7 @@
       <c r="AI292" s="5"/>
       <c r="AJ292" s="5"/>
     </row>
-    <row r="293" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -13032,7 +13092,7 @@
       <c r="AI293" s="5"/>
       <c r="AJ293" s="5"/>
     </row>
-    <row r="294" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -13070,7 +13130,7 @@
       <c r="AI294" s="5"/>
       <c r="AJ294" s="5"/>
     </row>
-    <row r="295" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -13108,7 +13168,7 @@
       <c r="AI295" s="5"/>
       <c r="AJ295" s="5"/>
     </row>
-    <row r="296" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -13146,7 +13206,7 @@
       <c r="AI296" s="5"/>
       <c r="AJ296" s="5"/>
     </row>
-    <row r="297" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -13184,7 +13244,7 @@
       <c r="AI297" s="5"/>
       <c r="AJ297" s="5"/>
     </row>
-    <row r="298" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -13222,7 +13282,7 @@
       <c r="AI298" s="5"/>
       <c r="AJ298" s="5"/>
     </row>
-    <row r="299" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -13260,7 +13320,7 @@
       <c r="AI299" s="5"/>
       <c r="AJ299" s="5"/>
     </row>
-    <row r="300" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -13298,7 +13358,7 @@
       <c r="AI300" s="5"/>
       <c r="AJ300" s="5"/>
     </row>
-    <row r="301" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -13336,7 +13396,7 @@
       <c r="AI301" s="5"/>
       <c r="AJ301" s="5"/>
     </row>
-    <row r="302" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -13374,7 +13434,7 @@
       <c r="AI302" s="5"/>
       <c r="AJ302" s="5"/>
     </row>
-    <row r="303" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -13412,7 +13472,7 @@
       <c r="AI303" s="5"/>
       <c r="AJ303" s="5"/>
     </row>
-    <row r="304" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -13450,7 +13510,7 @@
       <c r="AI304" s="5"/>
       <c r="AJ304" s="5"/>
     </row>
-    <row r="305" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -13488,7 +13548,7 @@
       <c r="AI305" s="5"/>
       <c r="AJ305" s="5"/>
     </row>
-    <row r="306" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -13526,7 +13586,7 @@
       <c r="AI306" s="5"/>
       <c r="AJ306" s="5"/>
     </row>
-    <row r="307" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -13564,7 +13624,7 @@
       <c r="AI307" s="5"/>
       <c r="AJ307" s="5"/>
     </row>
-    <row r="308" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -13602,7 +13662,7 @@
       <c r="AI308" s="5"/>
       <c r="AJ308" s="5"/>
     </row>
-    <row r="309" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -13640,7 +13700,7 @@
       <c r="AI309" s="5"/>
       <c r="AJ309" s="5"/>
     </row>
-    <row r="310" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -13678,7 +13738,7 @@
       <c r="AI310" s="5"/>
       <c r="AJ310" s="5"/>
     </row>
-    <row r="311" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -13716,7 +13776,7 @@
       <c r="AI311" s="5"/>
       <c r="AJ311" s="5"/>
     </row>
-    <row r="312" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -13754,7 +13814,7 @@
       <c r="AI312" s="5"/>
       <c r="AJ312" s="5"/>
     </row>
-    <row r="313" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -13792,7 +13852,7 @@
       <c r="AI313" s="5"/>
       <c r="AJ313" s="5"/>
     </row>
-    <row r="314" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -13830,7 +13890,7 @@
       <c r="AI314" s="5"/>
       <c r="AJ314" s="5"/>
     </row>
-    <row r="315" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -13868,7 +13928,7 @@
       <c r="AI315" s="5"/>
       <c r="AJ315" s="5"/>
     </row>
-    <row r="316" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -13906,7 +13966,7 @@
       <c r="AI316" s="5"/>
       <c r="AJ316" s="5"/>
     </row>
-    <row r="317" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -13944,7 +14004,7 @@
       <c r="AI317" s="5"/>
       <c r="AJ317" s="5"/>
     </row>
-    <row r="318" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -13982,7 +14042,7 @@
       <c r="AI318" s="5"/>
       <c r="AJ318" s="5"/>
     </row>
-    <row r="319" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -14020,7 +14080,7 @@
       <c r="AI319" s="5"/>
       <c r="AJ319" s="5"/>
     </row>
-    <row r="320" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -14058,7 +14118,7 @@
       <c r="AI320" s="5"/>
       <c r="AJ320" s="5"/>
     </row>
-    <row r="321" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -14096,7 +14156,7 @@
       <c r="AI321" s="5"/>
       <c r="AJ321" s="5"/>
     </row>
-    <row r="322" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -14134,7 +14194,7 @@
       <c r="AI322" s="5"/>
       <c r="AJ322" s="5"/>
     </row>
-    <row r="323" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -14172,7 +14232,7 @@
       <c r="AI323" s="5"/>
       <c r="AJ323" s="5"/>
     </row>
-    <row r="324" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -14210,7 +14270,7 @@
       <c r="AI324" s="5"/>
       <c r="AJ324" s="5"/>
     </row>
-    <row r="325" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -14248,7 +14308,7 @@
       <c r="AI325" s="5"/>
       <c r="AJ325" s="5"/>
     </row>
-    <row r="326" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -14286,7 +14346,7 @@
       <c r="AI326" s="5"/>
       <c r="AJ326" s="5"/>
     </row>
-    <row r="327" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -14324,7 +14384,7 @@
       <c r="AI327" s="5"/>
       <c r="AJ327" s="5"/>
     </row>
-    <row r="328" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -14362,7 +14422,7 @@
       <c r="AI328" s="5"/>
       <c r="AJ328" s="5"/>
     </row>
-    <row r="329" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -14400,7 +14460,7 @@
       <c r="AI329" s="5"/>
       <c r="AJ329" s="5"/>
     </row>
-    <row r="330" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -14438,7 +14498,7 @@
       <c r="AI330" s="5"/>
       <c r="AJ330" s="5"/>
     </row>
-    <row r="331" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -14476,7 +14536,7 @@
       <c r="AI331" s="5"/>
       <c r="AJ331" s="5"/>
     </row>
-    <row r="332" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -14514,7 +14574,7 @@
       <c r="AI332" s="5"/>
       <c r="AJ332" s="5"/>
     </row>
-    <row r="333" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -14552,7 +14612,7 @@
       <c r="AI333" s="5"/>
       <c r="AJ333" s="5"/>
     </row>
-    <row r="334" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -14590,7 +14650,7 @@
       <c r="AI334" s="5"/>
       <c r="AJ334" s="5"/>
     </row>
-    <row r="335" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -14628,7 +14688,7 @@
       <c r="AI335" s="5"/>
       <c r="AJ335" s="5"/>
     </row>
-    <row r="336" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -14666,7 +14726,7 @@
       <c r="AI336" s="5"/>
       <c r="AJ336" s="5"/>
     </row>
-    <row r="337" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -14704,7 +14764,7 @@
       <c r="AI337" s="5"/>
       <c r="AJ337" s="5"/>
     </row>
-    <row r="338" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -14742,7 +14802,7 @@
       <c r="AI338" s="5"/>
       <c r="AJ338" s="5"/>
     </row>
-    <row r="339" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -14780,7 +14840,7 @@
       <c r="AI339" s="5"/>
       <c r="AJ339" s="5"/>
     </row>
-    <row r="340" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -14818,7 +14878,7 @@
       <c r="AI340" s="5"/>
       <c r="AJ340" s="5"/>
     </row>
-    <row r="341" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -14856,7 +14916,7 @@
       <c r="AI341" s="5"/>
       <c r="AJ341" s="5"/>
     </row>
-    <row r="342" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -14894,7 +14954,7 @@
       <c r="AI342" s="5"/>
       <c r="AJ342" s="5"/>
     </row>
-    <row r="343" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -14932,7 +14992,7 @@
       <c r="AI343" s="5"/>
       <c r="AJ343" s="5"/>
     </row>
-    <row r="344" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -14970,7 +15030,7 @@
       <c r="AI344" s="5"/>
       <c r="AJ344" s="5"/>
     </row>
-    <row r="345" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -15008,7 +15068,7 @@
       <c r="AI345" s="5"/>
       <c r="AJ345" s="5"/>
     </row>
-    <row r="346" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -15046,7 +15106,7 @@
       <c r="AI346" s="5"/>
       <c r="AJ346" s="5"/>
     </row>
-    <row r="347" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -15084,7 +15144,7 @@
       <c r="AI347" s="5"/>
       <c r="AJ347" s="5"/>
     </row>
-    <row r="348" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -15122,7 +15182,7 @@
       <c r="AI348" s="5"/>
       <c r="AJ348" s="5"/>
     </row>
-    <row r="349" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -15160,7 +15220,7 @@
       <c r="AI349" s="5"/>
       <c r="AJ349" s="5"/>
     </row>
-    <row r="350" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -15198,7 +15258,7 @@
       <c r="AI350" s="5"/>
       <c r="AJ350" s="5"/>
     </row>
-    <row r="351" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -15236,7 +15296,7 @@
       <c r="AI351" s="5"/>
       <c r="AJ351" s="5"/>
     </row>
-    <row r="352" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -15274,7 +15334,7 @@
       <c r="AI352" s="5"/>
       <c r="AJ352" s="5"/>
     </row>
-    <row r="353" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -15312,7 +15372,7 @@
       <c r="AI353" s="5"/>
       <c r="AJ353" s="5"/>
     </row>
-    <row r="354" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -15350,7 +15410,7 @@
       <c r="AI354" s="5"/>
       <c r="AJ354" s="5"/>
     </row>
-    <row r="355" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -15388,7 +15448,7 @@
       <c r="AI355" s="5"/>
       <c r="AJ355" s="5"/>
     </row>
-    <row r="356" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -15426,7 +15486,7 @@
       <c r="AI356" s="5"/>
       <c r="AJ356" s="5"/>
     </row>
-    <row r="357" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -15464,7 +15524,7 @@
       <c r="AI357" s="5"/>
       <c r="AJ357" s="5"/>
     </row>
-    <row r="358" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -15502,7 +15562,7 @@
       <c r="AI358" s="5"/>
       <c r="AJ358" s="5"/>
     </row>
-    <row r="359" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -15540,7 +15600,7 @@
       <c r="AI359" s="5"/>
       <c r="AJ359" s="5"/>
     </row>
-    <row r="360" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -15578,7 +15638,7 @@
       <c r="AI360" s="5"/>
       <c r="AJ360" s="5"/>
     </row>
-    <row r="361" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -15616,7 +15676,7 @@
       <c r="AI361" s="5"/>
       <c r="AJ361" s="5"/>
     </row>
-    <row r="362" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -15654,7 +15714,7 @@
       <c r="AI362" s="5"/>
       <c r="AJ362" s="5"/>
     </row>
-    <row r="363" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -15692,7 +15752,7 @@
       <c r="AI363" s="5"/>
       <c r="AJ363" s="5"/>
     </row>
-    <row r="364" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -15730,7 +15790,7 @@
       <c r="AI364" s="5"/>
       <c r="AJ364" s="5"/>
     </row>
-    <row r="365" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -15768,7 +15828,7 @@
       <c r="AI365" s="5"/>
       <c r="AJ365" s="5"/>
     </row>
-    <row r="366" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -15806,7 +15866,7 @@
       <c r="AI366" s="5"/>
       <c r="AJ366" s="5"/>
     </row>
-    <row r="367" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -15844,7 +15904,7 @@
       <c r="AI367" s="5"/>
       <c r="AJ367" s="5"/>
     </row>
-    <row r="368" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -15882,7 +15942,7 @@
       <c r="AI368" s="5"/>
       <c r="AJ368" s="5"/>
     </row>
-    <row r="369" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -15920,7 +15980,7 @@
       <c r="AI369" s="5"/>
       <c r="AJ369" s="5"/>
     </row>
-    <row r="370" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -15958,7 +16018,7 @@
       <c r="AI370" s="5"/>
       <c r="AJ370" s="5"/>
     </row>
-    <row r="371" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -15996,7 +16056,7 @@
       <c r="AI371" s="5"/>
       <c r="AJ371" s="5"/>
     </row>
-    <row r="372" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -16034,7 +16094,7 @@
       <c r="AI372" s="5"/>
       <c r="AJ372" s="5"/>
     </row>
-    <row r="373" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -16072,7 +16132,7 @@
       <c r="AI373" s="5"/>
       <c r="AJ373" s="5"/>
     </row>
-    <row r="374" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -16110,7 +16170,7 @@
       <c r="AI374" s="5"/>
       <c r="AJ374" s="5"/>
     </row>
-    <row r="375" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -16148,7 +16208,7 @@
       <c r="AI375" s="5"/>
       <c r="AJ375" s="5"/>
     </row>
-    <row r="376" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -16186,7 +16246,7 @@
       <c r="AI376" s="5"/>
       <c r="AJ376" s="5"/>
     </row>
-    <row r="377" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -16224,7 +16284,7 @@
       <c r="AI377" s="5"/>
       <c r="AJ377" s="5"/>
     </row>
-    <row r="378" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -16262,7 +16322,7 @@
       <c r="AI378" s="5"/>
       <c r="AJ378" s="5"/>
     </row>
-    <row r="379" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -16300,7 +16360,7 @@
       <c r="AI379" s="5"/>
       <c r="AJ379" s="5"/>
     </row>
-    <row r="380" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -16338,7 +16398,7 @@
       <c r="AI380" s="5"/>
       <c r="AJ380" s="5"/>
     </row>
-    <row r="381" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -16376,7 +16436,7 @@
       <c r="AI381" s="5"/>
       <c r="AJ381" s="5"/>
     </row>
-    <row r="382" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -16414,7 +16474,7 @@
       <c r="AI382" s="5"/>
       <c r="AJ382" s="5"/>
     </row>
-    <row r="383" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -16452,7 +16512,7 @@
       <c r="AI383" s="5"/>
       <c r="AJ383" s="5"/>
     </row>
-    <row r="384" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -16490,7 +16550,7 @@
       <c r="AI384" s="5"/>
       <c r="AJ384" s="5"/>
     </row>
-    <row r="385" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -16528,7 +16588,7 @@
       <c r="AI385" s="5"/>
       <c r="AJ385" s="5"/>
     </row>
-    <row r="386" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -16566,7 +16626,7 @@
       <c r="AI386" s="5"/>
       <c r="AJ386" s="5"/>
     </row>
-    <row r="387" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -16604,7 +16664,7 @@
       <c r="AI387" s="5"/>
       <c r="AJ387" s="5"/>
     </row>
-    <row r="388" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -16642,7 +16702,7 @@
       <c r="AI388" s="5"/>
       <c r="AJ388" s="5"/>
     </row>
-    <row r="389" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -16680,7 +16740,7 @@
       <c r="AI389" s="5"/>
       <c r="AJ389" s="5"/>
     </row>
-    <row r="390" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -16718,7 +16778,7 @@
       <c r="AI390" s="5"/>
       <c r="AJ390" s="5"/>
     </row>
-    <row r="391" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -16756,7 +16816,7 @@
       <c r="AI391" s="5"/>
       <c r="AJ391" s="5"/>
     </row>
-    <row r="392" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -16794,7 +16854,7 @@
       <c r="AI392" s="5"/>
       <c r="AJ392" s="5"/>
     </row>
-    <row r="393" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -16832,7 +16892,7 @@
       <c r="AI393" s="5"/>
       <c r="AJ393" s="5"/>
     </row>
-    <row r="394" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -16870,7 +16930,7 @@
       <c r="AI394" s="5"/>
       <c r="AJ394" s="5"/>
     </row>
-    <row r="395" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -16908,7 +16968,7 @@
       <c r="AI395" s="5"/>
       <c r="AJ395" s="5"/>
     </row>
-    <row r="396" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -16946,7 +17006,7 @@
       <c r="AI396" s="5"/>
       <c r="AJ396" s="5"/>
     </row>
-    <row r="397" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -16984,7 +17044,7 @@
       <c r="AI397" s="5"/>
       <c r="AJ397" s="5"/>
     </row>
-    <row r="398" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -17022,7 +17082,7 @@
       <c r="AI398" s="5"/>
       <c r="AJ398" s="5"/>
     </row>
-    <row r="399" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -17060,7 +17120,7 @@
       <c r="AI399" s="5"/>
       <c r="AJ399" s="5"/>
     </row>
-    <row r="400" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -17098,7 +17158,7 @@
       <c r="AI400" s="5"/>
       <c r="AJ400" s="5"/>
     </row>
-    <row r="401" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -17136,7 +17196,7 @@
       <c r="AI401" s="5"/>
       <c r="AJ401" s="5"/>
     </row>
-    <row r="402" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -17174,7 +17234,7 @@
       <c r="AI402" s="5"/>
       <c r="AJ402" s="5"/>
     </row>
-    <row r="403" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -17212,7 +17272,7 @@
       <c r="AI403" s="5"/>
       <c r="AJ403" s="5"/>
     </row>
-    <row r="404" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -17250,7 +17310,7 @@
       <c r="AI404" s="5"/>
       <c r="AJ404" s="5"/>
     </row>
-    <row r="405" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -17288,7 +17348,7 @@
       <c r="AI405" s="5"/>
       <c r="AJ405" s="5"/>
     </row>
-    <row r="406" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -17326,7 +17386,7 @@
       <c r="AI406" s="5"/>
       <c r="AJ406" s="5"/>
     </row>
-    <row r="407" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -17364,7 +17424,7 @@
       <c r="AI407" s="5"/>
       <c r="AJ407" s="5"/>
     </row>
-    <row r="408" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -17402,7 +17462,7 @@
       <c r="AI408" s="5"/>
       <c r="AJ408" s="5"/>
     </row>
-    <row r="409" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -17440,7 +17500,7 @@
       <c r="AI409" s="5"/>
       <c r="AJ409" s="5"/>
     </row>
-    <row r="410" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -17478,7 +17538,7 @@
       <c r="AI410" s="5"/>
       <c r="AJ410" s="5"/>
     </row>
-    <row r="411" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -17516,7 +17576,7 @@
       <c r="AI411" s="5"/>
       <c r="AJ411" s="5"/>
     </row>
-    <row r="412" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -17554,7 +17614,7 @@
       <c r="AI412" s="5"/>
       <c r="AJ412" s="5"/>
     </row>
-    <row r="413" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -17592,7 +17652,7 @@
       <c r="AI413" s="5"/>
       <c r="AJ413" s="5"/>
     </row>
-    <row r="414" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -17630,7 +17690,7 @@
       <c r="AI414" s="5"/>
       <c r="AJ414" s="5"/>
     </row>
-    <row r="415" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -17668,7 +17728,7 @@
       <c r="AI415" s="5"/>
       <c r="AJ415" s="5"/>
     </row>
-    <row r="416" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -17706,7 +17766,7 @@
       <c r="AI416" s="5"/>
       <c r="AJ416" s="5"/>
     </row>
-    <row r="417" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -17744,7 +17804,7 @@
       <c r="AI417" s="5"/>
       <c r="AJ417" s="5"/>
     </row>
-    <row r="418" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -17782,7 +17842,7 @@
       <c r="AI418" s="5"/>
       <c r="AJ418" s="5"/>
     </row>
-    <row r="419" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -17820,7 +17880,7 @@
       <c r="AI419" s="5"/>
       <c r="AJ419" s="5"/>
     </row>
-    <row r="420" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -17858,7 +17918,7 @@
       <c r="AI420" s="5"/>
       <c r="AJ420" s="5"/>
     </row>
-    <row r="421" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -17896,7 +17956,7 @@
       <c r="AI421" s="5"/>
       <c r="AJ421" s="5"/>
     </row>
-    <row r="422" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -17934,7 +17994,7 @@
       <c r="AI422" s="5"/>
       <c r="AJ422" s="5"/>
     </row>
-    <row r="423" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -17972,7 +18032,7 @@
       <c r="AI423" s="5"/>
       <c r="AJ423" s="5"/>
     </row>
-    <row r="424" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -18010,7 +18070,7 @@
       <c r="AI424" s="5"/>
       <c r="AJ424" s="5"/>
     </row>
-    <row r="425" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -18048,7 +18108,7 @@
       <c r="AI425" s="5"/>
       <c r="AJ425" s="5"/>
     </row>
-    <row r="426" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -18086,7 +18146,7 @@
       <c r="AI426" s="5"/>
       <c r="AJ426" s="5"/>
     </row>
-    <row r="427" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -18124,7 +18184,7 @@
       <c r="AI427" s="5"/>
       <c r="AJ427" s="5"/>
     </row>
-    <row r="428" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -18162,7 +18222,7 @@
       <c r="AI428" s="5"/>
       <c r="AJ428" s="5"/>
     </row>
-    <row r="429" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -18200,7 +18260,7 @@
       <c r="AI429" s="5"/>
       <c r="AJ429" s="5"/>
     </row>
-    <row r="430" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -18238,7 +18298,7 @@
       <c r="AI430" s="5"/>
       <c r="AJ430" s="5"/>
     </row>
-    <row r="431" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -18276,7 +18336,7 @@
       <c r="AI431" s="5"/>
       <c r="AJ431" s="5"/>
     </row>
-    <row r="432" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -18314,7 +18374,7 @@
       <c r="AI432" s="5"/>
       <c r="AJ432" s="5"/>
     </row>
-    <row r="433" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -18352,7 +18412,7 @@
       <c r="AI433" s="5"/>
       <c r="AJ433" s="5"/>
     </row>
-    <row r="434" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -18390,7 +18450,7 @@
       <c r="AI434" s="5"/>
       <c r="AJ434" s="5"/>
     </row>
-    <row r="435" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -18428,7 +18488,7 @@
       <c r="AI435" s="5"/>
       <c r="AJ435" s="5"/>
     </row>
-    <row r="436" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -18466,7 +18526,7 @@
       <c r="AI436" s="5"/>
       <c r="AJ436" s="5"/>
     </row>
-    <row r="437" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -18504,7 +18564,7 @@
       <c r="AI437" s="5"/>
       <c r="AJ437" s="5"/>
     </row>
-    <row r="438" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -18542,7 +18602,7 @@
       <c r="AI438" s="5"/>
       <c r="AJ438" s="5"/>
     </row>
-    <row r="439" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -18580,7 +18640,7 @@
       <c r="AI439" s="5"/>
       <c r="AJ439" s="5"/>
     </row>
-    <row r="440" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -18618,7 +18678,7 @@
       <c r="AI440" s="5"/>
       <c r="AJ440" s="5"/>
     </row>
-    <row r="441" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -18656,7 +18716,7 @@
       <c r="AI441" s="5"/>
       <c r="AJ441" s="5"/>
     </row>
-    <row r="442" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -18694,7 +18754,7 @@
       <c r="AI442" s="5"/>
       <c r="AJ442" s="5"/>
     </row>
-    <row r="443" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -18732,7 +18792,7 @@
       <c r="AI443" s="5"/>
       <c r="AJ443" s="5"/>
     </row>
-    <row r="444" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -18770,7 +18830,7 @@
       <c r="AI444" s="5"/>
       <c r="AJ444" s="5"/>
     </row>
-    <row r="445" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -18808,7 +18868,7 @@
       <c r="AI445" s="5"/>
       <c r="AJ445" s="5"/>
     </row>
-    <row r="446" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -18846,7 +18906,7 @@
       <c r="AI446" s="5"/>
       <c r="AJ446" s="5"/>
     </row>
-    <row r="447" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -18884,7 +18944,7 @@
       <c r="AI447" s="5"/>
       <c r="AJ447" s="5"/>
     </row>
-    <row r="448" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A448" s="5"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
@@ -18922,7 +18982,7 @@
       <c r="AI448" s="5"/>
       <c r="AJ448" s="5"/>
     </row>
-    <row r="449" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A449" s="5"/>
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
@@ -18960,7 +19020,7 @@
       <c r="AI449" s="5"/>
       <c r="AJ449" s="5"/>
     </row>
-    <row r="450" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A450" s="5"/>
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
@@ -18998,7 +19058,7 @@
       <c r="AI450" s="5"/>
       <c r="AJ450" s="5"/>
     </row>
-    <row r="451" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A451" s="5"/>
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
@@ -19036,7 +19096,7 @@
       <c r="AI451" s="5"/>
       <c r="AJ451" s="5"/>
     </row>
-    <row r="452" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A452" s="5"/>
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
@@ -19074,7 +19134,7 @@
       <c r="AI452" s="5"/>
       <c r="AJ452" s="5"/>
     </row>
-    <row r="453" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A453" s="5"/>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -19112,7 +19172,7 @@
       <c r="AI453" s="5"/>
       <c r="AJ453" s="5"/>
     </row>
-    <row r="454" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A454" s="5"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -19150,7 +19210,7 @@
       <c r="AI454" s="5"/>
       <c r="AJ454" s="5"/>
     </row>
-    <row r="455" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A455" s="5"/>
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
@@ -19188,7 +19248,7 @@
       <c r="AI455" s="5"/>
       <c r="AJ455" s="5"/>
     </row>
-    <row r="456" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A456" s="5"/>
       <c r="B456" s="5"/>
       <c r="C456" s="5"/>
@@ -19226,7 +19286,7 @@
       <c r="AI456" s="5"/>
       <c r="AJ456" s="5"/>
     </row>
-    <row r="457" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A457" s="5"/>
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
@@ -19264,7 +19324,7 @@
       <c r="AI457" s="5"/>
       <c r="AJ457" s="5"/>
     </row>
-    <row r="458" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A458" s="5"/>
       <c r="B458" s="5"/>
       <c r="C458" s="5"/>
@@ -19302,7 +19362,7 @@
       <c r="AI458" s="5"/>
       <c r="AJ458" s="5"/>
     </row>
-    <row r="459" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A459" s="5"/>
       <c r="B459" s="5"/>
       <c r="C459" s="5"/>
@@ -19340,7 +19400,7 @@
       <c r="AI459" s="5"/>
       <c r="AJ459" s="5"/>
     </row>
-    <row r="460" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A460" s="5"/>
       <c r="B460" s="5"/>
       <c r="C460" s="5"/>
@@ -19378,7 +19438,7 @@
       <c r="AI460" s="5"/>
       <c r="AJ460" s="5"/>
     </row>
-    <row r="461" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A461" s="5"/>
       <c r="B461" s="5"/>
       <c r="C461" s="5"/>
@@ -19416,7 +19476,7 @@
       <c r="AI461" s="5"/>
       <c r="AJ461" s="5"/>
     </row>
-    <row r="462" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A462" s="5"/>
       <c r="B462" s="5"/>
       <c r="C462" s="5"/>
@@ -19454,7 +19514,7 @@
       <c r="AI462" s="5"/>
       <c r="AJ462" s="5"/>
     </row>
-    <row r="463" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A463" s="5"/>
       <c r="B463" s="5"/>
       <c r="C463" s="5"/>
@@ -19492,7 +19552,7 @@
       <c r="AI463" s="5"/>
       <c r="AJ463" s="5"/>
     </row>
-    <row r="464" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A464" s="5"/>
       <c r="B464" s="5"/>
       <c r="C464" s="5"/>
@@ -19530,7 +19590,7 @@
       <c r="AI464" s="5"/>
       <c r="AJ464" s="5"/>
     </row>
-    <row r="465" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A465" s="5"/>
       <c r="B465" s="5"/>
       <c r="C465" s="5"/>
@@ -19568,7 +19628,7 @@
       <c r="AI465" s="5"/>
       <c r="AJ465" s="5"/>
     </row>
-    <row r="466" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A466" s="5"/>
       <c r="B466" s="5"/>
       <c r="C466" s="5"/>
@@ -19606,7 +19666,7 @@
       <c r="AI466" s="5"/>
       <c r="AJ466" s="5"/>
     </row>
-    <row r="467" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A467" s="5"/>
       <c r="B467" s="5"/>
       <c r="C467" s="5"/>
@@ -19644,7 +19704,7 @@
       <c r="AI467" s="5"/>
       <c r="AJ467" s="5"/>
     </row>
-    <row r="468" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A468" s="5"/>
       <c r="B468" s="5"/>
       <c r="C468" s="5"/>
@@ -19682,7 +19742,7 @@
       <c r="AI468" s="5"/>
       <c r="AJ468" s="5"/>
     </row>
-    <row r="469" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A469" s="5"/>
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
@@ -19720,7 +19780,7 @@
       <c r="AI469" s="5"/>
       <c r="AJ469" s="5"/>
     </row>
-    <row r="470" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A470" s="5"/>
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
@@ -19758,7 +19818,7 @@
       <c r="AI470" s="5"/>
       <c r="AJ470" s="5"/>
     </row>
-    <row r="471" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A471" s="5"/>
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
@@ -19796,7 +19856,7 @@
       <c r="AI471" s="5"/>
       <c r="AJ471" s="5"/>
     </row>
-    <row r="472" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A472" s="5"/>
       <c r="B472" s="5"/>
       <c r="C472" s="5"/>
@@ -19834,7 +19894,7 @@
       <c r="AI472" s="5"/>
       <c r="AJ472" s="5"/>
     </row>
-    <row r="473" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A473" s="5"/>
       <c r="B473" s="5"/>
       <c r="C473" s="5"/>
@@ -19872,7 +19932,7 @@
       <c r="AI473" s="5"/>
       <c r="AJ473" s="5"/>
     </row>
-    <row r="474" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A474" s="5"/>
       <c r="B474" s="5"/>
       <c r="C474" s="5"/>
@@ -19910,7 +19970,7 @@
       <c r="AI474" s="5"/>
       <c r="AJ474" s="5"/>
     </row>
-    <row r="475" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A475" s="5"/>
       <c r="B475" s="5"/>
       <c r="C475" s="5"/>
@@ -19948,7 +20008,7 @@
       <c r="AI475" s="5"/>
       <c r="AJ475" s="5"/>
     </row>
-    <row r="476" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A476" s="5"/>
       <c r="B476" s="5"/>
       <c r="C476" s="5"/>
@@ -19986,7 +20046,7 @@
       <c r="AI476" s="5"/>
       <c r="AJ476" s="5"/>
     </row>
-    <row r="477" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A477" s="5"/>
       <c r="B477" s="5"/>
       <c r="C477" s="5"/>
@@ -20024,7 +20084,7 @@
       <c r="AI477" s="5"/>
       <c r="AJ477" s="5"/>
     </row>
-    <row r="478" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A478" s="5"/>
       <c r="B478" s="5"/>
       <c r="C478" s="5"/>
@@ -20062,7 +20122,7 @@
       <c r="AI478" s="5"/>
       <c r="AJ478" s="5"/>
     </row>
-    <row r="479" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A479" s="5"/>
       <c r="B479" s="5"/>
       <c r="C479" s="5"/>
@@ -20100,7 +20160,7 @@
       <c r="AI479" s="5"/>
       <c r="AJ479" s="5"/>
     </row>
-    <row r="480" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A480" s="5"/>
       <c r="B480" s="5"/>
       <c r="C480" s="5"/>
@@ -20138,7 +20198,7 @@
       <c r="AI480" s="5"/>
       <c r="AJ480" s="5"/>
     </row>
-    <row r="481" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A481" s="5"/>
       <c r="B481" s="5"/>
       <c r="C481" s="5"/>
@@ -20176,7 +20236,7 @@
       <c r="AI481" s="5"/>
       <c r="AJ481" s="5"/>
     </row>
-    <row r="482" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A482" s="5"/>
       <c r="B482" s="5"/>
       <c r="C482" s="5"/>
@@ -20214,7 +20274,7 @@
       <c r="AI482" s="5"/>
       <c r="AJ482" s="5"/>
     </row>
-    <row r="483" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A483" s="5"/>
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
@@ -20252,7 +20312,7 @@
       <c r="AI483" s="5"/>
       <c r="AJ483" s="5"/>
     </row>
-    <row r="484" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A484" s="5"/>
       <c r="B484" s="5"/>
       <c r="C484" s="5"/>
@@ -20290,7 +20350,7 @@
       <c r="AI484" s="5"/>
       <c r="AJ484" s="5"/>
     </row>
-    <row r="485" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A485" s="5"/>
       <c r="B485" s="5"/>
       <c r="C485" s="5"/>
@@ -20328,7 +20388,7 @@
       <c r="AI485" s="5"/>
       <c r="AJ485" s="5"/>
     </row>
-    <row r="486" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A486" s="5"/>
       <c r="B486" s="5"/>
       <c r="C486" s="5"/>
@@ -20366,7 +20426,7 @@
       <c r="AI486" s="5"/>
       <c r="AJ486" s="5"/>
     </row>
-    <row r="487" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A487" s="5"/>
       <c r="B487" s="5"/>
       <c r="C487" s="5"/>
@@ -20404,7 +20464,7 @@
       <c r="AI487" s="5"/>
       <c r="AJ487" s="5"/>
     </row>
-    <row r="488" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A488" s="5"/>
       <c r="B488" s="5"/>
       <c r="C488" s="5"/>
@@ -20442,7 +20502,7 @@
       <c r="AI488" s="5"/>
       <c r="AJ488" s="5"/>
     </row>
-    <row r="489" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A489" s="5"/>
       <c r="B489" s="5"/>
       <c r="C489" s="5"/>
@@ -20480,7 +20540,7 @@
       <c r="AI489" s="5"/>
       <c r="AJ489" s="5"/>
     </row>
-    <row r="490" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A490" s="5"/>
       <c r="B490" s="5"/>
       <c r="C490" s="5"/>
@@ -20518,7 +20578,7 @@
       <c r="AI490" s="5"/>
       <c r="AJ490" s="5"/>
     </row>
-    <row r="491" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A491" s="5"/>
       <c r="B491" s="5"/>
       <c r="C491" s="5"/>
@@ -20556,7 +20616,7 @@
       <c r="AI491" s="5"/>
       <c r="AJ491" s="5"/>
     </row>
-    <row r="492" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A492" s="5"/>
       <c r="B492" s="5"/>
       <c r="C492" s="5"/>
@@ -20594,7 +20654,7 @@
       <c r="AI492" s="5"/>
       <c r="AJ492" s="5"/>
     </row>
-    <row r="493" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A493" s="5"/>
       <c r="B493" s="5"/>
       <c r="C493" s="5"/>
@@ -20632,7 +20692,7 @@
       <c r="AI493" s="5"/>
       <c r="AJ493" s="5"/>
     </row>
-    <row r="494" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A494" s="5"/>
       <c r="B494" s="5"/>
       <c r="C494" s="5"/>
@@ -20670,7 +20730,7 @@
       <c r="AI494" s="5"/>
       <c r="AJ494" s="5"/>
     </row>
-    <row r="495" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A495" s="5"/>
       <c r="B495" s="5"/>
       <c r="C495" s="5"/>
@@ -20708,7 +20768,7 @@
       <c r="AI495" s="5"/>
       <c r="AJ495" s="5"/>
     </row>
-    <row r="496" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A496" s="5"/>
       <c r="B496" s="5"/>
       <c r="C496" s="5"/>
@@ -20746,7 +20806,7 @@
       <c r="AI496" s="5"/>
       <c r="AJ496" s="5"/>
     </row>
-    <row r="497" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A497" s="5"/>
       <c r="B497" s="5"/>
       <c r="C497" s="5"/>
@@ -20784,7 +20844,7 @@
       <c r="AI497" s="5"/>
       <c r="AJ497" s="5"/>
     </row>
-    <row r="498" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A498" s="5"/>
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
@@ -20822,7 +20882,7 @@
       <c r="AI498" s="5"/>
       <c r="AJ498" s="5"/>
     </row>
-    <row r="499" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A499" s="5"/>
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
@@ -20860,7 +20920,7 @@
       <c r="AI499" s="5"/>
       <c r="AJ499" s="5"/>
     </row>
-    <row r="500" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A500" s="5"/>
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
@@ -20898,7 +20958,7 @@
       <c r="AI500" s="5"/>
       <c r="AJ500" s="5"/>
     </row>
-    <row r="501" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A501" s="5"/>
       <c r="B501" s="5"/>
       <c r="C501" s="5"/>
@@ -20936,7 +20996,7 @@
       <c r="AI501" s="5"/>
       <c r="AJ501" s="5"/>
     </row>
-    <row r="502" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A502" s="5"/>
       <c r="B502" s="5"/>
       <c r="C502" s="5"/>
@@ -20974,7 +21034,7 @@
       <c r="AI502" s="5"/>
       <c r="AJ502" s="5"/>
     </row>
-    <row r="503" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A503" s="5"/>
       <c r="B503" s="5"/>
       <c r="C503" s="5"/>
@@ -21012,7 +21072,7 @@
       <c r="AI503" s="5"/>
       <c r="AJ503" s="5"/>
     </row>
-    <row r="504" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A504" s="5"/>
       <c r="B504" s="5"/>
       <c r="C504" s="5"/>
@@ -21050,7 +21110,7 @@
       <c r="AI504" s="5"/>
       <c r="AJ504" s="5"/>
     </row>
-    <row r="505" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A505" s="5"/>
       <c r="B505" s="5"/>
       <c r="C505" s="5"/>
@@ -21088,7 +21148,7 @@
       <c r="AI505" s="5"/>
       <c r="AJ505" s="5"/>
     </row>
-    <row r="506" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A506" s="5"/>
       <c r="B506" s="5"/>
       <c r="C506" s="5"/>
@@ -21126,7 +21186,7 @@
       <c r="AI506" s="5"/>
       <c r="AJ506" s="5"/>
     </row>
-    <row r="507" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A507" s="5"/>
       <c r="B507" s="5"/>
       <c r="C507" s="5"/>
@@ -21164,7 +21224,7 @@
       <c r="AI507" s="5"/>
       <c r="AJ507" s="5"/>
     </row>
-    <row r="508" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A508" s="5"/>
       <c r="B508" s="5"/>
       <c r="C508" s="5"/>
@@ -21202,7 +21262,7 @@
       <c r="AI508" s="5"/>
       <c r="AJ508" s="5"/>
     </row>
-    <row r="509" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A509" s="5"/>
       <c r="B509" s="5"/>
       <c r="C509" s="5"/>
@@ -21240,7 +21300,7 @@
       <c r="AI509" s="5"/>
       <c r="AJ509" s="5"/>
     </row>
-    <row r="510" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A510" s="5"/>
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
@@ -21278,7 +21338,7 @@
       <c r="AI510" s="5"/>
       <c r="AJ510" s="5"/>
     </row>
-    <row r="511" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A511" s="5"/>
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
@@ -21316,7 +21376,7 @@
       <c r="AI511" s="5"/>
       <c r="AJ511" s="5"/>
     </row>
-    <row r="512" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A512" s="5"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -21354,7 +21414,7 @@
       <c r="AI512" s="5"/>
       <c r="AJ512" s="5"/>
     </row>
-    <row r="513" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A513" s="5"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -21392,7 +21452,7 @@
       <c r="AI513" s="5"/>
       <c r="AJ513" s="5"/>
     </row>
-    <row r="514" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A514" s="5"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -21430,7 +21490,7 @@
       <c r="AI514" s="5"/>
       <c r="AJ514" s="5"/>
     </row>
-    <row r="515" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A515" s="5"/>
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
@@ -21468,7 +21528,7 @@
       <c r="AI515" s="5"/>
       <c r="AJ515" s="5"/>
     </row>
-    <row r="516" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A516" s="5"/>
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
@@ -21506,7 +21566,7 @@
       <c r="AI516" s="5"/>
       <c r="AJ516" s="5"/>
     </row>
-    <row r="517" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A517" s="5"/>
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
@@ -21544,7 +21604,7 @@
       <c r="AI517" s="5"/>
       <c r="AJ517" s="5"/>
     </row>
-    <row r="518" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A518" s="5"/>
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
@@ -21582,7 +21642,7 @@
       <c r="AI518" s="5"/>
       <c r="AJ518" s="5"/>
     </row>
-    <row r="519" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A519" s="5"/>
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
@@ -21620,7 +21680,7 @@
       <c r="AI519" s="5"/>
       <c r="AJ519" s="5"/>
     </row>
-    <row r="520" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A520" s="5"/>
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
@@ -21658,7 +21718,7 @@
       <c r="AI520" s="5"/>
       <c r="AJ520" s="5"/>
     </row>
-    <row r="521" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A521" s="5"/>
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
@@ -21696,7 +21756,7 @@
       <c r="AI521" s="5"/>
       <c r="AJ521" s="5"/>
     </row>
-    <row r="522" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A522" s="5"/>
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
@@ -21734,7 +21794,7 @@
       <c r="AI522" s="5"/>
       <c r="AJ522" s="5"/>
     </row>
-    <row r="523" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A523" s="5"/>
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
@@ -21772,7 +21832,7 @@
       <c r="AI523" s="5"/>
       <c r="AJ523" s="5"/>
     </row>
-    <row r="524" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A524" s="5"/>
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
@@ -21810,7 +21870,7 @@
       <c r="AI524" s="5"/>
       <c r="AJ524" s="5"/>
     </row>
-    <row r="525" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A525" s="5"/>
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
@@ -21848,7 +21908,7 @@
       <c r="AI525" s="5"/>
       <c r="AJ525" s="5"/>
     </row>
-    <row r="526" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A526" s="5"/>
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
@@ -21886,7 +21946,7 @@
       <c r="AI526" s="5"/>
       <c r="AJ526" s="5"/>
     </row>
-    <row r="527" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A527" s="5"/>
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
@@ -21924,7 +21984,7 @@
       <c r="AI527" s="5"/>
       <c r="AJ527" s="5"/>
     </row>
-    <row r="528" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A528" s="5"/>
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
@@ -21962,7 +22022,7 @@
       <c r="AI528" s="5"/>
       <c r="AJ528" s="5"/>
     </row>
-    <row r="529" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A529" s="5"/>
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
@@ -22000,7 +22060,7 @@
       <c r="AI529" s="5"/>
       <c r="AJ529" s="5"/>
     </row>
-    <row r="530" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A530" s="5"/>
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
@@ -22038,7 +22098,7 @@
       <c r="AI530" s="5"/>
       <c r="AJ530" s="5"/>
     </row>
-    <row r="531" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A531" s="5"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -22076,7 +22136,7 @@
       <c r="AI531" s="5"/>
       <c r="AJ531" s="5"/>
     </row>
-    <row r="532" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A532" s="5"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -22114,7 +22174,7 @@
       <c r="AI532" s="5"/>
       <c r="AJ532" s="5"/>
     </row>
-    <row r="533" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A533" s="5"/>
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
@@ -22152,7 +22212,7 @@
       <c r="AI533" s="5"/>
       <c r="AJ533" s="5"/>
     </row>
-    <row r="534" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:36" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A534" s="5"/>
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
@@ -22192,16 +22252,17 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="A38" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A7" r:id="rId1" xr:uid="{E335443C-9EAD-4D66-A678-0020664FD919}"/>
+    <hyperlink ref="A38" r:id="rId2" xr:uid="{6CAED3A3-CB48-4DA0-B494-AF1C41BE9208}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -22213,7 +22274,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -22306,9 +22367,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
